--- a/projects/NZIPL/docs/trade_data/latest_2024/NZIPL_2024_RoleStage_Exports_USDmn.xlsx
+++ b/projects/NZIPL/docs/trade_data/latest_2024/NZIPL_2024_RoleStage_Exports_USDmn.xlsx
@@ -94,7 +94,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-10</t>
+    <t xml:space="preserve">2026-07-11</t>
   </si>
   <si>
     <t xml:space="preserve">ISO3</t>
@@ -7692,7 +7692,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1175.66</v>
+        <v>2351.321</v>
       </c>
     </row>
     <row r="9">
@@ -7811,7 +7811,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>43.684</v>
+        <v>87.369</v>
       </c>
     </row>
     <row r="16">
@@ -7930,7 +7930,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>912.322</v>
+        <v>1824.643</v>
       </c>
     </row>
     <row r="23">
@@ -8049,7 +8049,7 @@
         <v>38</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.974</v>
+        <v>1.947</v>
       </c>
     </row>
     <row r="30">
@@ -8168,7 +8168,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>4.668</v>
+        <v>9.337</v>
       </c>
     </row>
     <row r="37">
@@ -8287,7 +8287,7 @@
         <v>38</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>93.038</v>
+        <v>186.076</v>
       </c>
     </row>
     <row r="44">
@@ -8406,7 +8406,7 @@
         <v>38</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2.99</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="51">
@@ -8525,7 +8525,7 @@
         <v>38</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.437</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="58">
@@ -8644,7 +8644,7 @@
         <v>38</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>18.281</v>
+        <v>36.562</v>
       </c>
     </row>
     <row r="65">
@@ -8763,7 +8763,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>20.275</v>
+        <v>40.551</v>
       </c>
     </row>
     <row r="72">
@@ -8882,7 +8882,7 @@
         <v>38</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>10.142</v>
+        <v>20.284</v>
       </c>
     </row>
     <row r="79">
@@ -9001,7 +9001,7 @@
         <v>38</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>277.383</v>
+        <v>554.766</v>
       </c>
     </row>
     <row r="86">
@@ -9120,7 +9120,7 @@
         <v>38</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>0.611</v>
+        <v>1.223</v>
       </c>
     </row>
     <row r="93">
@@ -9239,7 +9239,7 @@
         <v>38</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>0.054</v>
+        <v>0.109</v>
       </c>
     </row>
     <row r="100">
@@ -9358,7 +9358,7 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>202.174</v>
+        <v>404.348</v>
       </c>
     </row>
     <row r="107">
@@ -9477,7 +9477,7 @@
         <v>38</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>3.279</v>
+        <v>6.558</v>
       </c>
     </row>
     <row r="114">
@@ -9834,7 +9834,7 @@
         <v>38</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>4.501</v>
+        <v>9.002</v>
       </c>
     </row>
     <row r="135">
@@ -9953,7 +9953,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>4.85</v>
+        <v>9.7</v>
       </c>
     </row>
     <row r="142">
@@ -10072,7 +10072,7 @@
         <v>38</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>0.331</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="149">
@@ -10191,15 +10191,15 @@
         <v>38</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>3.085</v>
+        <v>6.17</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B156" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C156" t="s">
         <v>31</v>
@@ -10208,15 +10208,15 @@
         <v>32</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>127.085</v>
+        <v>686.397</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B157" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C157" t="s">
         <v>33</v>
@@ -10225,15 +10225,15 @@
         <v>34</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>2.705</v>
+        <v>24.445</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B158" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C158" t="s">
         <v>33</v>
@@ -10242,15 +10242,15 @@
         <v>35</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>2263.883</v>
+        <v>1777.943</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B159" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C159" t="s">
         <v>33</v>
@@ -10259,15 +10259,15 @@
         <v>36</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>3243.402</v>
+        <v>4048.119</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B160" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C160" t="s">
         <v>37</v>
@@ -10276,15 +10276,15 @@
         <v>34</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>332.086</v>
+        <v>374.027</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B161" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C161" t="s">
         <v>37</v>
@@ -10293,15 +10293,15 @@
         <v>36</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>609.848</v>
+        <v>764.68</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B162" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C162" t="s">
         <v>38</v>
@@ -10310,15 +10310,15 @@
         <v>38</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>0.623</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B163" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C163" t="s">
         <v>31</v>
@@ -10327,15 +10327,15 @@
         <v>32</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>686.397</v>
+        <v>127.085</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B164" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C164" t="s">
         <v>33</v>
@@ -10344,15 +10344,15 @@
         <v>34</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>24.445</v>
+        <v>2.705</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B165" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C165" t="s">
         <v>33</v>
@@ -10361,15 +10361,15 @@
         <v>35</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>1777.943</v>
+        <v>2263.883</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B166" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C166" t="s">
         <v>33</v>
@@ -10378,15 +10378,15 @@
         <v>36</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>4048.119</v>
+        <v>3243.402</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B167" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C167" t="s">
         <v>37</v>
@@ -10395,15 +10395,15 @@
         <v>34</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>374.027</v>
+        <v>332.086</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B168" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C168" t="s">
         <v>37</v>
@@ -10412,15 +10412,15 @@
         <v>36</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>764.68</v>
+        <v>609.848</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B169" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C169" t="s">
         <v>38</v>
@@ -10429,7 +10429,7 @@
         <v>38</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>0.398</v>
+        <v>1.245</v>
       </c>
     </row>
     <row r="170">
@@ -10548,7 +10548,7 @@
         <v>38</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>2.842</v>
+        <v>5.685</v>
       </c>
     </row>
     <row r="177">
@@ -10667,7 +10667,7 @@
         <v>38</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>1.056</v>
+        <v>2.112</v>
       </c>
     </row>
     <row r="184">
@@ -10888,7 +10888,7 @@
         <v>38</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>0.134</v>
+        <v>0.267</v>
       </c>
     </row>
     <row r="197">
@@ -11280,7 +11280,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>34365.009</v>
+        <v>34745.634</v>
       </c>
     </row>
     <row r="9">
@@ -11399,7 +11399,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>14.538</v>
+        <v>16.307</v>
       </c>
     </row>
     <row r="16">
@@ -11518,7 +11518,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2423.166</v>
+        <v>2450.63</v>
       </c>
     </row>
     <row r="23">
@@ -11637,7 +11637,7 @@
         <v>38</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>3352.304</v>
+        <v>3392.069</v>
       </c>
     </row>
     <row r="30">
@@ -11756,7 +11756,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1902.524</v>
+        <v>1957.702</v>
       </c>
     </row>
     <row r="37">
@@ -11875,7 +11875,7 @@
         <v>38</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2489.095</v>
+        <v>2496.488</v>
       </c>
     </row>
     <row r="44">
@@ -12113,7 +12113,7 @@
         <v>38</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>476.424</v>
+        <v>482.1</v>
       </c>
     </row>
     <row r="58">
@@ -12232,7 +12232,7 @@
         <v>38</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>121.716</v>
+        <v>134.422</v>
       </c>
     </row>
     <row r="65">
@@ -12351,7 +12351,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>239.185</v>
+        <v>262.103</v>
       </c>
     </row>
     <row r="72">
@@ -12470,7 +12470,7 @@
         <v>38</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>231.445</v>
+        <v>239.126</v>
       </c>
     </row>
     <row r="79">
@@ -12589,7 +12589,7 @@
         <v>38</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>508.506</v>
+        <v>523.418</v>
       </c>
     </row>
     <row r="86">
@@ -12708,7 +12708,7 @@
         <v>38</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>0.882</v>
+        <v>1.068</v>
       </c>
     </row>
     <row r="93">
@@ -12827,7 +12827,7 @@
         <v>38</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>66.481</v>
+        <v>71.77</v>
       </c>
     </row>
     <row r="100">
@@ -12946,7 +12946,7 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>358.477</v>
+        <v>365.849</v>
       </c>
     </row>
     <row r="107">
@@ -13065,7 +13065,7 @@
         <v>38</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>118.357</v>
+        <v>125.547</v>
       </c>
     </row>
     <row r="114">
@@ -13184,7 +13184,7 @@
         <v>38</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>231.884</v>
+        <v>232.632</v>
       </c>
     </row>
     <row r="121">
@@ -13303,7 +13303,7 @@
         <v>38</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>282.299</v>
+        <v>293.628</v>
       </c>
     </row>
     <row r="128">
@@ -13422,7 +13422,7 @@
         <v>38</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>94.668</v>
+        <v>105.193</v>
       </c>
     </row>
     <row r="135">
@@ -13541,7 +13541,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>3.315</v>
+        <v>5.798</v>
       </c>
     </row>
     <row r="142">
@@ -13660,7 +13660,7 @@
         <v>38</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>54.127</v>
+        <v>60.827</v>
       </c>
     </row>
     <row r="149">
@@ -13779,7 +13779,7 @@
         <v>38</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>751.819</v>
+        <v>755.161</v>
       </c>
     </row>
     <row r="156">
@@ -13898,7 +13898,7 @@
         <v>38</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>0.557</v>
+        <v>1.051</v>
       </c>
     </row>
     <row r="163">
@@ -14017,7 +14017,7 @@
         <v>38</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>3709.907</v>
+        <v>3731.436</v>
       </c>
     </row>
     <row r="170">
@@ -14136,7 +14136,7 @@
         <v>38</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>354.179</v>
+        <v>356.324</v>
       </c>
     </row>
     <row r="177">
@@ -14255,7 +14255,7 @@
         <v>38</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>82.245</v>
+        <v>99.17</v>
       </c>
     </row>
     <row r="184">
@@ -14374,7 +14374,7 @@
         <v>38</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>298.208</v>
+        <v>302.09</v>
       </c>
     </row>
     <row r="191">
@@ -14493,7 +14493,7 @@
         <v>38</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>114.983</v>
+        <v>117.766</v>
       </c>
     </row>
     <row r="198">
@@ -14612,7 +14612,7 @@
         <v>38</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>144.167</v>
+        <v>148.641</v>
       </c>
     </row>
     <row r="205">
@@ -14731,7 +14731,7 @@
         <v>38</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>45.921</v>
+        <v>49.822</v>
       </c>
     </row>
   </sheetData>
@@ -14851,7 +14851,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3263.574</v>
+        <v>3699.885</v>
       </c>
     </row>
     <row r="7">
@@ -14936,7 +14936,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1949.007</v>
+        <v>3849.985</v>
       </c>
     </row>
     <row r="12">
@@ -15021,7 +15021,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>685.718</v>
+        <v>1361.028</v>
       </c>
     </row>
     <row r="17">
@@ -15106,7 +15106,7 @@
         <v>38</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>7.087</v>
+        <v>12.454</v>
       </c>
     </row>
     <row r="22">
@@ -15191,7 +15191,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>210.503</v>
+        <v>409.702</v>
       </c>
     </row>
     <row r="27">
@@ -15276,7 +15276,7 @@
         <v>38</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2166.584</v>
+        <v>4167.523</v>
       </c>
     </row>
     <row r="32">
@@ -15361,7 +15361,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>305.457</v>
+        <v>609.38</v>
       </c>
     </row>
     <row r="37">
@@ -15446,7 +15446,7 @@
         <v>38</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>101.585</v>
+        <v>198.577</v>
       </c>
     </row>
     <row r="42">
@@ -15531,15 +15531,15 @@
         <v>38</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>336.413</v>
+        <v>583.52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
         <v>31</v>
@@ -15548,15 +15548,15 @@
         <v>32</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1649.308</v>
+        <v>387.712</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
         <v>33</v>
@@ -15565,15 +15565,15 @@
         <v>34</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>9.149</v>
+        <v>218.393</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
         <v>33</v>
@@ -15582,15 +15582,15 @@
         <v>35</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>9508.719</v>
+        <v>3278.951</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C50" t="s">
         <v>37</v>
@@ -15599,15 +15599,15 @@
         <v>34</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>253.784</v>
+        <v>843.726</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B51" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C51" t="s">
         <v>38</v>
@@ -15616,15 +15616,15 @@
         <v>38</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>62.534</v>
+        <v>3864.593</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B52" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C52" t="s">
         <v>31</v>
@@ -15633,15 +15633,15 @@
         <v>32</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>387.712</v>
+        <v>1649.308</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C53" t="s">
         <v>33</v>
@@ -15650,15 +15650,15 @@
         <v>34</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>218.393</v>
+        <v>9.149</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C54" t="s">
         <v>33</v>
@@ -15667,15 +15667,15 @@
         <v>35</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>3278.951</v>
+        <v>9508.719</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
         <v>37</v>
@@ -15684,15 +15684,15 @@
         <v>34</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>843.726</v>
+        <v>253.784</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C56" t="s">
         <v>38</v>
@@ -15701,7 +15701,7 @@
         <v>38</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>1954.552</v>
+        <v>62.59</v>
       </c>
     </row>
     <row r="57">
@@ -15786,7 +15786,7 @@
         <v>38</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>347.636</v>
+        <v>626.606</v>
       </c>
     </row>
     <row r="62">
@@ -16041,7 +16041,7 @@
         <v>38</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>1000.754</v>
+        <v>1889.262</v>
       </c>
     </row>
     <row r="77">
@@ -16126,7 +16126,7 @@
         <v>38</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>27.786</v>
+        <v>53.226</v>
       </c>
     </row>
     <row r="82">
@@ -16296,7 +16296,7 @@
         <v>38</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>234.989</v>
+        <v>288.183</v>
       </c>
     </row>
     <row r="92">
@@ -16381,7 +16381,7 @@
         <v>38</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>5.906</v>
+        <v>5.971</v>
       </c>
     </row>
     <row r="97">
@@ -16466,7 +16466,7 @@
         <v>38</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>117.687</v>
+        <v>235.202</v>
       </c>
     </row>
     <row r="102">
@@ -16551,7 +16551,7 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>447.182</v>
+        <v>894.261</v>
       </c>
     </row>
     <row r="107">
@@ -16636,15 +16636,15 @@
         <v>38</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>65.6</v>
+        <v>131.2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B112" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C112" t="s">
         <v>31</v>
@@ -16653,15 +16653,15 @@
         <v>32</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>815.788</v>
+        <v>78.959</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B113" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C113" t="s">
         <v>33</v>
@@ -16670,15 +16670,15 @@
         <v>34</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>36.538</v>
+        <v>47.706</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B114" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C114" t="s">
         <v>33</v>
@@ -16687,15 +16687,15 @@
         <v>35</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>1076.72</v>
+        <v>2059.011</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B115" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C115" t="s">
         <v>37</v>
@@ -16704,15 +16704,15 @@
         <v>34</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>1311.806</v>
+        <v>1903.618</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="B116" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C116" t="s">
         <v>38</v>
@@ -16721,15 +16721,15 @@
         <v>38</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>28.948</v>
+        <v>444.497</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B117" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C117" t="s">
         <v>31</v>
@@ -16738,15 +16738,15 @@
         <v>32</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>78.959</v>
+        <v>815.788</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B118" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C118" t="s">
         <v>33</v>
@@ -16755,15 +16755,15 @@
         <v>34</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>47.706</v>
+        <v>36.538</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B119" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C119" t="s">
         <v>33</v>
@@ -16772,15 +16772,15 @@
         <v>35</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>2059.011</v>
+        <v>1076.72</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B120" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C120" t="s">
         <v>37</v>
@@ -16789,15 +16789,15 @@
         <v>34</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>1903.618</v>
+        <v>1311.806</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B121" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C121" t="s">
         <v>38</v>
@@ -16806,7 +16806,7 @@
         <v>38</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>258.134</v>
+        <v>57.601</v>
       </c>
     </row>
     <row r="122">
@@ -16976,7 +16976,7 @@
         <v>38</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>64.314</v>
+        <v>128.481</v>
       </c>
     </row>
     <row r="132">
@@ -17061,7 +17061,7 @@
         <v>38</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>34.958</v>
+        <v>57.209</v>
       </c>
     </row>
     <row r="137">
@@ -17146,7 +17146,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>8.569</v>
+        <v>16.863</v>
       </c>
     </row>
     <row r="142">
@@ -17231,7 +17231,7 @@
         <v>38</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>18.892</v>
+        <v>27.569</v>
       </c>
     </row>
     <row r="147">
@@ -17368,7 +17368,7 @@
         <v>32</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2370.109</v>
+        <v>2374.694</v>
       </c>
     </row>
     <row r="3">
@@ -17470,7 +17470,7 @@
         <v>32</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5825.583</v>
+        <v>5873.264</v>
       </c>
     </row>
     <row r="9">
@@ -17776,7 +17776,7 @@
         <v>32</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>94620.154</v>
+        <v>94692.754</v>
       </c>
     </row>
     <row r="27">
@@ -17878,7 +17878,7 @@
         <v>32</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>10635.204</v>
+        <v>10714.753</v>
       </c>
     </row>
     <row r="33">
@@ -18082,7 +18082,7 @@
         <v>32</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1034.921</v>
+        <v>1039.156</v>
       </c>
     </row>
     <row r="45">
@@ -18184,7 +18184,7 @@
         <v>32</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>3947.554</v>
+        <v>4149.325</v>
       </c>
     </row>
     <row r="51">
@@ -18286,7 +18286,7 @@
         <v>32</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>36054.102</v>
+        <v>36082.257</v>
       </c>
     </row>
     <row r="57">
@@ -18490,7 +18490,7 @@
         <v>32</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>335.086</v>
+        <v>335.786</v>
       </c>
     </row>
     <row r="69">
@@ -18592,7 +18592,7 @@
         <v>32</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>1192.778</v>
+        <v>1225.974</v>
       </c>
     </row>
     <row r="75">
@@ -18898,7 +18898,7 @@
         <v>32</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>254.355</v>
+        <v>255.76</v>
       </c>
     </row>
     <row r="93">
@@ -19204,7 +19204,7 @@
         <v>32</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>3523.353</v>
+        <v>3849.187</v>
       </c>
     </row>
     <row r="111">
@@ -19408,7 +19408,7 @@
         <v>32</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>2890.031</v>
+        <v>2927.582</v>
       </c>
     </row>
     <row r="123">
@@ -19510,7 +19510,7 @@
         <v>32</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>1076.943</v>
+        <v>1113.274</v>
       </c>
     </row>
     <row r="129">
@@ -20020,7 +20020,7 @@
         <v>32</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>1361.483</v>
+        <v>1411.102</v>
       </c>
     </row>
     <row r="159">
@@ -20565,7 +20565,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>297.208</v>
+        <v>594.416</v>
       </c>
     </row>
     <row r="9">
@@ -20684,7 +20684,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>66.377</v>
+        <v>132.754</v>
       </c>
     </row>
     <row r="16">
@@ -20803,7 +20803,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>77.315</v>
+        <v>154.629</v>
       </c>
     </row>
     <row r="23">
@@ -20922,7 +20922,7 @@
         <v>38</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>116.312</v>
+        <v>232.624</v>
       </c>
     </row>
     <row r="30">
@@ -21041,7 +21041,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>41.935</v>
+        <v>83.87</v>
       </c>
     </row>
     <row r="37">
@@ -21160,7 +21160,7 @@
         <v>38</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>54.331</v>
+        <v>108.662</v>
       </c>
     </row>
     <row r="44">
@@ -21279,7 +21279,7 @@
         <v>38</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>22.261</v>
+        <v>44.521</v>
       </c>
     </row>
     <row r="51">
@@ -21398,7 +21398,7 @@
         <v>38</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>16.666</v>
+        <v>33.331</v>
       </c>
     </row>
     <row r="58">
@@ -21517,7 +21517,7 @@
         <v>38</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>9.588</v>
+        <v>19.175</v>
       </c>
     </row>
     <row r="65">
@@ -21636,7 +21636,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>2.4</v>
+        <v>4.799</v>
       </c>
     </row>
     <row r="72">
@@ -21755,7 +21755,7 @@
         <v>38</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>6.339</v>
+        <v>12.677</v>
       </c>
     </row>
     <row r="79">
@@ -21874,7 +21874,7 @@
         <v>38</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>13.436</v>
+        <v>26.873</v>
       </c>
     </row>
     <row r="86">
@@ -21993,7 +21993,7 @@
         <v>38</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>6.527</v>
+        <v>13.054</v>
       </c>
     </row>
     <row r="93">
@@ -22112,7 +22112,7 @@
         <v>38</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>2.129</v>
+        <v>4.259</v>
       </c>
     </row>
     <row r="100">
@@ -22231,7 +22231,7 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>0.474</v>
+        <v>0.949</v>
       </c>
     </row>
     <row r="107">
@@ -22350,7 +22350,7 @@
         <v>38</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>8.296</v>
+        <v>16.592</v>
       </c>
     </row>
     <row r="114">
@@ -22469,7 +22469,7 @@
         <v>38</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>0.3</v>
+        <v>0.601</v>
       </c>
     </row>
     <row r="121">
@@ -22588,7 +22588,7 @@
         <v>38</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>28.935</v>
+        <v>57.869</v>
       </c>
     </row>
     <row r="128">
@@ -22707,7 +22707,7 @@
         <v>38</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>2.766</v>
+        <v>5.532</v>
       </c>
     </row>
     <row r="135">
@@ -22826,7 +22826,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>1.526</v>
+        <v>3.051</v>
       </c>
     </row>
     <row r="142">
@@ -22945,7 +22945,7 @@
         <v>38</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>4.939</v>
+        <v>9.879</v>
       </c>
     </row>
     <row r="149">
@@ -23064,7 +23064,7 @@
         <v>38</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>6.63</v>
+        <v>13.261</v>
       </c>
     </row>
     <row r="156">
@@ -23183,7 +23183,7 @@
         <v>38</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>4.7</v>
+        <v>9.401</v>
       </c>
     </row>
     <row r="163">
@@ -23302,7 +23302,7 @@
         <v>38</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>10.137</v>
+        <v>20.274</v>
       </c>
     </row>
     <row r="170">
@@ -23421,7 +23421,7 @@
         <v>38</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>6.442</v>
+        <v>12.884</v>
       </c>
     </row>
     <row r="177">
@@ -23540,7 +23540,7 @@
         <v>38</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>4.661</v>
+        <v>9.323</v>
       </c>
     </row>
     <row r="184">
@@ -23659,7 +23659,7 @@
         <v>38</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>1.557</v>
+        <v>3.115</v>
       </c>
     </row>
     <row r="191">
@@ -23778,7 +23778,7 @@
         <v>38</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>11.945</v>
+        <v>23.89</v>
       </c>
     </row>
     <row r="198">
@@ -23897,7 +23897,7 @@
         <v>38</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>0.595</v>
+        <v>1.189</v>
       </c>
     </row>
     <row r="205">
@@ -24016,7 +24016,7 @@
         <v>38</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>3.142</v>
+        <v>6.284</v>
       </c>
     </row>
   </sheetData>
@@ -31346,7 +31346,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2019.991</v>
+        <v>3575.839</v>
       </c>
     </row>
     <row r="7">
@@ -31431,7 +31431,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>253.559</v>
+        <v>467.75</v>
       </c>
     </row>
     <row r="12">
@@ -31516,7 +31516,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>79.606</v>
+        <v>126.008</v>
       </c>
     </row>
     <row r="17">
@@ -31601,7 +31601,7 @@
         <v>38</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>160.338</v>
+        <v>275.177</v>
       </c>
     </row>
     <row r="22">
@@ -31686,7 +31686,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.178</v>
+        <v>0.355</v>
       </c>
     </row>
     <row r="27">
@@ -31771,7 +31771,7 @@
         <v>38</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>52.544</v>
+        <v>69.845</v>
       </c>
     </row>
     <row r="32">
@@ -31856,7 +31856,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>8.459</v>
+        <v>11.817</v>
       </c>
     </row>
     <row r="37">
@@ -32026,7 +32026,7 @@
         <v>38</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>3.627</v>
+        <v>7.068</v>
       </c>
     </row>
     <row r="47">
@@ -32111,7 +32111,7 @@
         <v>38</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>35.136</v>
+        <v>51.504</v>
       </c>
     </row>
     <row r="52">
@@ -32196,7 +32196,7 @@
         <v>38</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>18.474</v>
+        <v>27.667</v>
       </c>
     </row>
     <row r="57">
@@ -32366,7 +32366,7 @@
         <v>38</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>8.533</v>
+        <v>12.228</v>
       </c>
     </row>
     <row r="67">
@@ -32451,7 +32451,7 @@
         <v>38</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>9.41</v>
+        <v>16.771</v>
       </c>
     </row>
     <row r="72">
@@ -32536,7 +32536,7 @@
         <v>38</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>15.933</v>
+        <v>18.207</v>
       </c>
     </row>
     <row r="77">
@@ -32621,7 +32621,7 @@
         <v>38</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>27.321</v>
+        <v>46.474</v>
       </c>
     </row>
     <row r="82">
@@ -32706,7 +32706,7 @@
         <v>38</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>21.509</v>
+        <v>32.713</v>
       </c>
     </row>
     <row r="87">
@@ -32791,7 +32791,7 @@
         <v>38</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>29.639</v>
+        <v>42.355</v>
       </c>
     </row>
     <row r="92">
@@ -32961,7 +32961,7 @@
         <v>38</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>0.247</v>
+        <v>0.325</v>
       </c>
     </row>
     <row r="102">
@@ -33046,15 +33046,15 @@
         <v>38</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>23.234</v>
+        <v>34.539</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B107" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C107" t="s">
         <v>31</v>
@@ -33063,15 +33063,15 @@
         <v>32</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>184.344</v>
+        <v>2860.912</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B108" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C108" t="s">
         <v>33</v>
@@ -33080,15 +33080,15 @@
         <v>35</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>5048.048</v>
+        <v>39.209</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B109" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C109" t="s">
         <v>37</v>
@@ -33097,15 +33097,15 @@
         <v>34</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>169.692</v>
+        <v>30.877</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B110" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C110" t="s">
         <v>37</v>
@@ -33114,15 +33114,15 @@
         <v>36</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>0</v>
+        <v>7.601</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B111" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C111" t="s">
         <v>38</v>
@@ -33131,15 +33131,15 @@
         <v>38</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>0.065</v>
+        <v>291.622</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C112" t="s">
         <v>31</v>
@@ -33148,15 +33148,15 @@
         <v>32</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>2860.912</v>
+        <v>184.344</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C113" t="s">
         <v>33</v>
@@ -33165,15 +33165,15 @@
         <v>35</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>39.209</v>
+        <v>5048.048</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C114" t="s">
         <v>37</v>
@@ -33182,15 +33182,15 @@
         <v>34</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>30.877</v>
+        <v>169.692</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B115" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C115" t="s">
         <v>37</v>
@@ -33199,15 +33199,15 @@
         <v>36</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>7.601</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="B116" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C116" t="s">
         <v>38</v>
@@ -33216,7 +33216,7 @@
         <v>38</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>149.612</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="117">
@@ -33301,7 +33301,7 @@
         <v>38</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>61.697</v>
+        <v>91.671</v>
       </c>
     </row>
     <row r="122">
@@ -33386,7 +33386,7 @@
         <v>38</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>29.42</v>
+        <v>55.296</v>
       </c>
     </row>
     <row r="127">
@@ -33471,15 +33471,15 @@
         <v>38</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>6.733</v>
+        <v>8.612</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B132" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C132" t="s">
         <v>31</v>
@@ -33488,15 +33488,15 @@
         <v>32</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>124.697</v>
+        <v>1.405</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B133" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C133" t="s">
         <v>33</v>
@@ -33505,15 +33505,15 @@
         <v>35</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>165.709</v>
+        <v>488.815</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B134" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C134" t="s">
         <v>37</v>
@@ -33522,15 +33522,15 @@
         <v>34</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>840.036</v>
+        <v>235.204</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B135" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C135" t="s">
         <v>37</v>
@@ -33539,15 +33539,15 @@
         <v>36</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>3.206</v>
+        <v>6.996</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B136" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C136" t="s">
         <v>38</v>
@@ -33556,15 +33556,15 @@
         <v>38</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>7.165</v>
+        <v>60.982</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B137" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C137" t="s">
         <v>31</v>
@@ -33573,15 +33573,15 @@
         <v>32</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>1.405</v>
+        <v>124.697</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B138" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C138" t="s">
         <v>33</v>
@@ -33590,15 +33590,15 @@
         <v>35</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>488.815</v>
+        <v>165.709</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B139" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C139" t="s">
         <v>37</v>
@@ -33607,15 +33607,15 @@
         <v>34</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>235.204</v>
+        <v>840.036</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B140" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C140" t="s">
         <v>37</v>
@@ -33624,15 +33624,15 @@
         <v>36</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>6.996</v>
+        <v>3.206</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="B141" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="C141" t="s">
         <v>38</v>
@@ -33641,7 +33641,7 @@
         <v>38</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>33.989</v>
+        <v>11.123</v>
       </c>
     </row>
     <row r="142">
@@ -33726,7 +33726,7 @@
         <v>38</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>6.859</v>
+        <v>10.438</v>
       </c>
     </row>
     <row r="147">
@@ -33811,7 +33811,7 @@
         <v>38</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>5.599</v>
+        <v>7.995</v>
       </c>
     </row>
   </sheetData>
@@ -33965,7 +33965,7 @@
         <v>38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6.825</v>
+        <v>7.933</v>
       </c>
     </row>
     <row r="9">
@@ -34441,7 +34441,7 @@
         <v>38</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>38.934</v>
+        <v>39.123</v>
       </c>
     </row>
     <row r="37">
@@ -34764,7 +34764,7 @@
         <v>38</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>14.398</v>
+        <v>14.617</v>
       </c>
     </row>
     <row r="56">
@@ -35342,7 +35342,7 @@
         <v>38</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>242.619</v>
+        <v>324.261</v>
       </c>
     </row>
     <row r="90">
@@ -36039,7 +36039,7 @@
         <v>38</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>0.219</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="131">
@@ -37093,7 +37093,7 @@
         <v>38</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>0.089</v>
+        <v>0.177</v>
       </c>
     </row>
     <row r="193">
